--- a/Slots/H045_超級鑽石/文件/101015_腳本規格.xlsx
+++ b/Slots/H045_超級鑽石/文件/101015_腳本規格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhinshen\Mine\個人工作區\工作區\Slots\H045_超級鑽石\文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF3844C-4E0B-4CDE-A2BF-9E92361B9325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D945C0E5-2DA6-47B8-B6CA-024A432E840D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="79">
   <si>
     <t>H045 超級鑽石（101015）表演腳本表 — 92A 版（待填）</t>
   </si>
@@ -271,6 +271,14 @@
   </si>
   <si>
     <t>728364350,28173,35826,23563,1544487,894158,63936,0,1,0,48175,24357,6469721520,7,1326271,921063,1263733,1561666,588327,58711,1,0,0,0,55456,3,0,0,0,26799,267521,191298,511905,81798,76760,54454,4,706074,1625495,1358859,1250849,1525673,10463,47353,6676,1,10,10,5,5,6,6,2,1,2,0,1,0,8,1240859,1250529,1461371,1666225,497304,17086,24272,27992,892178,63503,445489,999020,11596,1409,9485,5,424574,614162,1376425,770058,459116,52033,1,1,1,0,45361,10810,954558,974854,851824,24650,13387,21877,41465,343392,792047,347242,968993,627384,94926,773369,756547,77043,32451,35678,2,57186,59650,719716,862262,958700,26110,98047,1,0,0,97885,1,0,0,0,4601207592,1,3,0,0,0,0,1,0,2,568700,1669345,1779147,1138005,465319,94357,3,0,1,0,15862,15503,1,3,7,4,1,0,3,3,0,0,0,4,962992,363372,97676,1659497,876099,77282,0,1,1,0,72103,0,0,0,5666,8,243,607901,825422,892047,291579,21972,7400,1095748432,2,770701,1237348,1401755,1109953,508957,17158,54328,2,1,0,0,27077,91,7,232676,280616,48865,93952,333170,495024,185799,397369,778571,492519,779760,744168,55961,1,0,41497,22745,5,4,0,5,10,2,7,1,5,0,3,0,2,2,1,0,16,93,246301,172450,172835,796443,836782,198407,191961,644276,190665,171915,85028,81745,0,13311,66694,0,0,0,87,163,274582,26421,202547,232697,426750,460505,196478,489143,61026,94573,1,0,64028,1,0,5,270655,430643,1480376,490863,1287936,99115,1,1,1,0,42985,97512,2,1,0,8717122117,0,1,1,1,2,1,0,7,31754,30665,377080,861408,1373626,92706,3,2,1,0,9638,58568,1,1,0,0,1,6,2,0,1,4,0,0,0,0</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>994871843,4,1115101,898399,226883,1539257,1684319,41457,0,0,1,0,49927,13340,26,223,21883,591088,947190,842894,416560,623531,554521,3939,572744,897232,32481,97336,1,0,42925,55,177,843938,913545,104819,510463,116457,493082,209250,61391,1,0,10963,46405,561551,128123,889565,813617,34556,974680,890509,768920,78651,37871,150850,695006,932711,41724,219870,87596,1,0,69690,514805,905607,801430,901483,70297,88961,49905,52,159,851236,584529,103870,43883,52661,53295</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>998164068,1,1059545,661409,354785,1481421,742519,43907,2,1,1,0,90653,2,2,1,0,592,53,231,51,213,370354,474274,920818,57663,69,195,20498,864477,293286,263279,157702,246466,449806,711860,458203,566331,51037,0,0,37759,39341,654996,62019,537372,147530,420855,815738,622444,233732,376254,3080,55440,0,0,37134,555828,326039,895583,524200,507534,48460,73370,18573</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -730,11 +738,15 @@
       <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="6" t="str">
+      <c r="B6" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="5">
+        <v>11.25</v>
+      </c>
+      <c r="D6" s="6">
         <f t="shared" ref="D6:D13" si="0">IF(C6="","",C6/F6)</f>
-        <v/>
+        <v>11.25</v>
       </c>
       <c r="E6" s="7">
         <v>1</v>
@@ -747,11 +759,15 @@
       <c r="A7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="6" t="str">
+      <c r="B7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="5">
+        <v>11.25</v>
+      </c>
+      <c r="D7" s="6">
         <f t="shared" si="0"/>
-        <v/>
+        <v>11.25</v>
       </c>
       <c r="E7" s="7">
         <v>1</v>
@@ -798,11 +814,15 @@
       <c r="A10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="6" t="str">
+      <c r="B10" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" s="5">
+        <v>22.45</v>
+      </c>
+      <c r="D10" s="6">
         <f t="shared" si="0"/>
-        <v/>
+        <v>11.225</v>
       </c>
       <c r="E10" s="7">
         <v>1</v>
@@ -815,11 +835,15 @@
       <c r="A11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="6" t="str">
+      <c r="B11" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="5">
+        <v>22.45</v>
+      </c>
+      <c r="D11" s="6">
         <f t="shared" si="0"/>
-        <v/>
+        <v>11.225</v>
       </c>
       <c r="E11" s="7">
         <v>1</v>
@@ -913,7 +937,7 @@
         <v>47.5</v>
       </c>
       <c r="D20" s="6">
-        <f t="shared" ref="D20:D31" si="1">IF(C20="","",C20/F20)</f>
+        <f t="shared" ref="D20:D28" si="1">IF(C20="","",C20/F20)</f>
         <v>0.95</v>
       </c>
       <c r="E20" s="5">

--- a/Slots/H045_超級鑽石/文件/101015_腳本規格.xlsx
+++ b/Slots/H045_超級鑽石/文件/101015_腳本規格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhinshen\Mine\個人工作區\工作區\Slots\H045_超級鑽石\文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D945C0E5-2DA6-47B8-B6CA-024A432E840D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B9470B-7C16-4338-935F-4DBEB04C67B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="84">
   <si>
     <t>H045 超級鑽石（101015）表演腳本表 — 92A 版（待填）</t>
   </si>
@@ -279,6 +279,106 @@
   </si>
   <si>
     <t>998164068,1,1059545,661409,354785,1481421,742519,43907,2,1,1,0,90653,2,2,1,0,592,53,231,51,213,370354,474274,920818,57663,69,195,20498,864477,293286,263279,157702,246466,449806,711860,458203,566331,51037,0,0,37759,39341,654996,62019,537372,147530,420855,815738,622444,233732,376254,3080,55440,0,0,37134,555828,326039,895583,524200,507534,48460,73370,18573</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>新手體驗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> NB Jackpot Game B</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>新手體驗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> NB Base Game A</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>新手體驗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> NB Base Game B</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>新手體驗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> EB Base Game A</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>新手體驗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> EB Base Game B</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -286,7 +386,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -319,6 +419,18 @@
       <sz val="12"/>
       <name val="Courier New"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Courier New"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="5">
@@ -371,7 +483,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -383,6 +495,7 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -735,8 +848,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.6" customHeight="1">
-      <c r="A6" s="5" t="s">
-        <v>9</v>
+      <c r="A6" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>77</v>
@@ -756,8 +869,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.6" customHeight="1">
-      <c r="A7" s="5" t="s">
-        <v>10</v>
+      <c r="A7" s="11" t="s">
+        <v>81</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>77</v>
@@ -794,8 +907,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.6" customHeight="1">
-      <c r="A9" s="5" t="s">
-        <v>12</v>
+      <c r="A9" s="11" t="s">
+        <v>79</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -811,8 +924,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.6" customHeight="1">
-      <c r="A10" s="5" t="s">
-        <v>13</v>
+      <c r="A10" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>78</v>
@@ -832,8 +945,8 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.6" customHeight="1">
-      <c r="A11" s="5" t="s">
-        <v>14</v>
+      <c r="A11" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>78</v>
